--- a/artfynd/A 40815-2025 artfynd.xlsx
+++ b/artfynd/A 40815-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,6 +915,557 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128589034</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100753</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Holmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>486324</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7005543</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128587683</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104016</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mårtensbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>486685</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7005522</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128587765</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100660</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mårtensbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>486665</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7005518</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128587858</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97448</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Holmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>486607</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7005532</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128612406</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Holmen, Holmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>486752</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7005552</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40815-2025 artfynd.xlsx
+++ b/artfynd/A 40815-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>128589034</v>
       </c>
       <c r="B4" t="n">
-        <v>100753</v>
+        <v>100761</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>128587683</v>
       </c>
       <c r="B5" t="n">
-        <v>104016</v>
+        <v>104028</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>128587765</v>
       </c>
       <c r="B6" t="n">
-        <v>100660</v>
+        <v>100668</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>128587858</v>
       </c>
       <c r="B7" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>128612406</v>
       </c>
       <c r="B8" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40815-2025 artfynd.xlsx
+++ b/artfynd/A 40815-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>128589034</v>
       </c>
       <c r="B4" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>128587683</v>
       </c>
       <c r="B5" t="n">
-        <v>104028</v>
+        <v>104036</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>128587765</v>
       </c>
       <c r="B6" t="n">
-        <v>100668</v>
+        <v>100674</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>128587858</v>
       </c>
       <c r="B7" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40815-2025 artfynd.xlsx
+++ b/artfynd/A 40815-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>128589034</v>
       </c>
       <c r="B4" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>128587683</v>
       </c>
       <c r="B5" t="n">
-        <v>104036</v>
+        <v>104048</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>128587765</v>
       </c>
       <c r="B6" t="n">
-        <v>100674</v>
+        <v>100679</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>128587858</v>
       </c>
       <c r="B7" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>128612406</v>
       </c>
       <c r="B8" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40815-2025 artfynd.xlsx
+++ b/artfynd/A 40815-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>128589034</v>
       </c>
       <c r="B4" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>128587683</v>
       </c>
       <c r="B5" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>128587765</v>
       </c>
       <c r="B6" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40815-2025 artfynd.xlsx
+++ b/artfynd/A 40815-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>128589034</v>
       </c>
       <c r="B4" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>128587683</v>
       </c>
       <c r="B5" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>128587765</v>
       </c>
       <c r="B6" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>128587858</v>
       </c>
       <c r="B7" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40815-2025 artfynd.xlsx
+++ b/artfynd/A 40815-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>128589034</v>
       </c>
       <c r="B4" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>128587683</v>
       </c>
       <c r="B5" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>128587765</v>
       </c>
       <c r="B6" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>128587858</v>
       </c>
       <c r="B7" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>128612406</v>
       </c>
       <c r="B8" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40815-2025 artfynd.xlsx
+++ b/artfynd/A 40815-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>128589034</v>
       </c>
       <c r="B4" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>128587683</v>
       </c>
       <c r="B5" t="n">
-        <v>104087</v>
+        <v>104093</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>128587765</v>
       </c>
       <c r="B6" t="n">
-        <v>100713</v>
+        <v>100719</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>128587858</v>
       </c>
       <c r="B7" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>128612406</v>
       </c>
       <c r="B8" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40815-2025 artfynd.xlsx
+++ b/artfynd/A 40815-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>128589034</v>
       </c>
       <c r="B4" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>128587683</v>
       </c>
       <c r="B5" t="n">
-        <v>104093</v>
+        <v>104100</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>128587765</v>
       </c>
       <c r="B6" t="n">
-        <v>100719</v>
+        <v>100726</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>128587858</v>
       </c>
       <c r="B7" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40815-2025 artfynd.xlsx
+++ b/artfynd/A 40815-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>128589034</v>
       </c>
       <c r="B4" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>128587683</v>
       </c>
       <c r="B5" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>128587765</v>
       </c>
       <c r="B6" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>128587858</v>
       </c>
       <c r="B7" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>128612406</v>
       </c>
       <c r="B8" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40815-2025 artfynd.xlsx
+++ b/artfynd/A 40815-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>128589034</v>
       </c>
       <c r="B4" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>128587683</v>
       </c>
       <c r="B5" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>128587765</v>
       </c>
       <c r="B6" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>128587858</v>
       </c>
       <c r="B7" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>128612406</v>
       </c>
       <c r="B8" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40815-2025 artfynd.xlsx
+++ b/artfynd/A 40815-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>128589034</v>
       </c>
       <c r="B4" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>128587683</v>
       </c>
       <c r="B5" t="n">
-        <v>104114</v>
+        <v>104119</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>128587765</v>
       </c>
       <c r="B6" t="n">
-        <v>100740</v>
+        <v>100745</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>128587858</v>
       </c>
       <c r="B7" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>128612406</v>
       </c>
       <c r="B8" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40815-2025 artfynd.xlsx
+++ b/artfynd/A 40815-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>128589034</v>
       </c>
       <c r="B4" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>128587683</v>
       </c>
       <c r="B5" t="n">
-        <v>104119</v>
+        <v>104127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>128587765</v>
       </c>
       <c r="B6" t="n">
-        <v>100745</v>
+        <v>100753</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>128587858</v>
       </c>
       <c r="B7" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>128612406</v>
       </c>
       <c r="B8" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40815-2025 artfynd.xlsx
+++ b/artfynd/A 40815-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104404337</v>
+        <v>128930815</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +708,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+          <t>Låga vid Spikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487047.1228372749</v>
+        <v>486469</v>
       </c>
       <c r="R2" t="n">
-        <v>7005689.464990998</v>
+        <v>7005547</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,27 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,33 +761,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104404338</v>
+        <v>114816630</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,38 +791,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+          <t>Holmen, Holmen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487047.1174076039</v>
+        <v>486674</v>
       </c>
       <c r="R3" t="n">
-        <v>7005688.110218263</v>
+        <v>7005506</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,27 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,64 +866,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128589034</v>
+        <v>128612406</v>
       </c>
       <c r="B4" t="n">
-        <v>100847</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Holmen, Jmt</t>
+          <t>Holmen, Holmen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486324</v>
+        <v>486752</v>
       </c>
       <c r="R4" t="n">
-        <v>7005543</v>
+        <v>7005552</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,22 +943,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,22 +973,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128587683</v>
+        <v>104403585</v>
       </c>
       <c r="B5" t="n">
-        <v>104127</v>
+        <v>99456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,41 +996,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>219880</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mårtensbodarna, Jmt</t>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486685</v>
+        <v>486522</v>
       </c>
       <c r="R5" t="n">
-        <v>7005522</v>
+        <v>7005567</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,22 +1059,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:26</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:26</t>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,22 +1084,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128587765</v>
+        <v>128588340</v>
       </c>
       <c r="B6" t="n">
-        <v>100753</v>
+        <v>99456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,41 +1107,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>219880</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mårtensbodarna, Jmt</t>
+          <t>Holmen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486665</v>
+        <v>486508</v>
       </c>
       <c r="R6" t="n">
-        <v>7005518</v>
+        <v>7005556</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,7 +1170,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1180,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,7 +1210,7 @@
         <v>128587858</v>
       </c>
       <c r="B7" t="n">
-        <v>97530</v>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,48 +1318,52 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128612406</v>
+        <v>128588489</v>
       </c>
       <c r="B8" t="n">
-        <v>80140</v>
+        <v>97983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Holmen, Holmen, Jmt</t>
+          <t>Holmen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486752</v>
+        <v>486471</v>
       </c>
       <c r="R8" t="n">
-        <v>7005552</v>
+        <v>7005575</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,22 +1387,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,15 +1417,2124 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128588949</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Holmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>486417</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7005549</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128588989</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Holmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>486371</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7005573</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>104403074</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>486564</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7005581</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>104403079</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>486434</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7005578</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128587683</v>
+      </c>
+      <c r="B13" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mårtensbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>486685</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7005522</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128589108</v>
+      </c>
+      <c r="B14" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Holmen, Holmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>486305</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7005582</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>104404011</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>486469</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7005536</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>104404012</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>486483</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7005543</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>104404013</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>486490</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7005544</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>104404014</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>486495</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7005544</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>104404015</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>486508</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7005558</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>104404016</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>486522</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7005566</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>104404017</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>486535</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7005559</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128587618</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mårtensbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>486657</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7005511</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128588284</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Holmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>486512</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7005543</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128589034</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Holmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>486324</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7005543</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128589094</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Holmen, Holmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>486306</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7005579</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128587596</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mårtensbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>486657</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7005511</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128587765</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mårtensbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>486665</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7005518</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40815-2025 artfynd.xlsx
+++ b/artfynd/A 40815-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128930815</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114816630</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128612406</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104403585</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128588340</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1315,6 +1345,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128587858</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128588489</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1537,6 +1577,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128588949</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1648,6 +1693,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128588989</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1759,6 +1809,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104403074</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1870,6 +1925,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104403079</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1981,6 +2041,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128587683</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2092,6 +2157,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128589108</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2203,6 +2273,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104404011</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2314,6 +2389,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104404012</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2425,6 +2505,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104404013</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2536,6 +2621,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104404014</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2647,6 +2737,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104404015</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2758,6 +2853,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104404016</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2869,6 +2969,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104404017</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2980,6 +3085,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128587618</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3091,6 +3201,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128588284</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3202,6 +3317,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128589034</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3313,6 +3433,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128589094</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3424,6 +3549,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128587596</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3535,8 +3665,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128587765</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>